--- a/Result/profitability/3537.xlsx
+++ b/Result/profitability/3537.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.19</v>
       </c>
       <c r="M2" t="n">
-        <v>0.61</v>
+        <v>0.6662499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>13.63125</v>
+        <v>13.72875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6849999999999999</v>
+        <v>0.6812499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>13.4075</v>
+        <v>13.51625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.95</v>
       </c>
       <c r="M4" t="n">
-        <v>0.69375</v>
+        <v>0.6462499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>11.86375</v>
+        <v>11.3525</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.52</v>
       </c>
       <c r="M5" t="n">
-        <v>0.605</v>
+        <v>0.8587499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>11.62875</v>
+        <v>11.94375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.79</v>
       </c>
       <c r="M6" t="n">
-        <v>0.85125</v>
+        <v>0.80125</v>
       </c>
       <c r="N6" t="n">
-        <v>11.33875</v>
+        <v>11.53375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6525</v>
+        <v>0.6074999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>10.8225</v>
+        <v>10.81</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.78</v>
       </c>
       <c r="M8" t="n">
-        <v>0.59875</v>
+        <v>0.5449999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>10.29875</v>
+        <v>10.02375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>0.66</v>
       </c>
       <c r="M9" t="n">
-        <v>0.52125</v>
+        <v>0.5212499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>9.385000000000002</v>
+        <v>9.385</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.5974999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>9.13125</v>
+        <v>9.131250000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.29</v>
       </c>
       <c r="M12" t="n">
-        <v>0.515</v>
+        <v>0.5149999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>10.275</v>
@@ -2029,7 +2029,7 @@
         <v>0.4324999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>9.418749999999999</v>
+        <v>9.418750000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3537</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>800</v>
+      </c>
+      <c r="D75" t="n">
+        <v>686</v>
+      </c>
+      <c r="E75" t="n">
+        <v>114</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>62</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.70%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>60</v>
+      </c>
+      <c r="K75" t="n">
+        <v>48</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.3125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3359375</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1339013998782714</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.720338983050847</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2152006831767719</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
